--- a/docs/status-delivery-kendala-jul2026.xlsx
+++ b/docs/status-delivery-kendala-jul2026.xlsx
@@ -16,14 +16,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EO (ARKA-AIM)'!$A$4:$F$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FASHION (Levi''s-EBR)'!$A$4:$F$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Menunggu Klien'!$A$4:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Menunggu Klien'!$A$4:$B$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="234">
   <si>
     <t>EO (ARKA-AIM)</t>
   </si>
@@ -100,372 +100,381 @@
     <t>Bank masuk/keluar masih lewat COA perantara</t>
   </si>
   <si>
+    <t>Sebagian Selesai</t>
+  </si>
+  <si>
+    <t>Keluhan klien BENAR — vonis 'tidak reproduce' 30-Jul keliru. payment_account_id NULL bukan berarti langsung ke akun bank; Odoo jatuh ke jalur berikutnya, dan jalur itu mengarah ke Outstanding Receipts/Payments — COA perantara yang dimaksud. Company 1 (AIM) kini LANGSUNG ke akun bank. Company 2 (ARKA) masih perantara, menunggu keputusan Finance karena sudah ada 5 payment terposting lewat sana</t>
+  </si>
+  <si>
+    <t>Company 1: bill -&gt; Register Payment via BCA1 -&gt; paid, liquidity 1103019270, tanpa perantara. Sebelumnya company 1 tidak bisa membuat payment sama sekali (3 jalur pencarian akun outstanding kosong semua)</t>
+  </si>
+  <si>
+    <t>#117</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Purchase report keluar Trial Balance</t>
+  </si>
+  <si>
+    <t>Report code tidak terdaftar di dispatcher sehingga jatuh ke fallback Trial Balance</t>
+  </si>
+  <si>
+    <t>prd_levis_begbal 69 baris; prd_arkaaim 9 baris</t>
+  </si>
+  <si>
+    <t>5a405ab</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Jurnal DP masuk ke COA penjualan</t>
+  </si>
+  <si>
+    <t>downpayment_account_id diarahkan ke 2108100001 Advances from customers</t>
+  </si>
+  <si>
+    <t>Diterapkan pada 2 company; re-run script melaporkan OK / 0 changes</t>
+  </si>
+  <si>
+    <t>8db557e</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Akses closing period belum tersedia</t>
+  </si>
+  <si>
+    <t>Butuh konfirmasi periode mana yang ditutup — lock date memblokir posting</t>
+  </si>
+  <si>
+    <t>fiscalyear_lock_date &amp; tax_lock_date NULL di kedua company</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Nilai perolehan asset selisih vs report accounting</t>
+  </si>
+  <si>
+    <t>Ditahan</t>
+  </si>
+  <si>
+    <t>DITAHAN menunggu konfirmasi. Ternyata DUA komponen, bukan satu</t>
+  </si>
+  <si>
+    <t>Perolehan: register 27.145.108.236 vs GL 27.110.131.391 = selisih 34.976.845. Accum-dep: 6.786.277.002,84 vs GL 7.341.288.299 = selisih +/- 555.011.296</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>No document depresiasi per bulan belum muncul</t>
+  </si>
+  <si>
+    <t>Kode SELESAI &amp; teruji. POSTING PRODUKSI DITAHAN menunggu keputusan klien. Akarnya bukan penomoran: jurnal belum pernah dibuat sama sekali</t>
+  </si>
+  <si>
+    <t>Uji di trn_arkaaim_begbal: 3.320 baris -&gt; 1 jurnal 565.523.083,57; GL accum-dep bergerak persis sebesar itu; reverse 1 baris tidak mengubah jurnal bulanan</t>
+  </si>
+  <si>
+    <t>d1c8952</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Sales report kosong padahal ada di detail beginning balance</t>
+  </si>
+  <si>
+    <t>Wizard dapat pilihan Sumber Data: Invoice+POS atau Akun Pendapatan (GL). Dibuat sebagai pilihan basis, bukan sumber ketiga, agar tidak double-count</t>
+  </si>
+  <si>
+    <t>Basis GL 735.585.585 = revenue GL independen (selisih 0,00); basis dokumen hanya 150.000.000</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PPh withholding belum otomatis per kode objek</t>
+  </si>
+  <si>
+    <t>Engine sudah ada tapi registry kosong; 107 kode objek dimuat + modul di-upgrade</t>
+  </si>
+  <si>
+    <t>107 kategori + 214 rule (107 x 2 company), 0 rule tanpa akun, 0 SKIP</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Setting due date belum sesuai ketentuan Erajaya</t>
+  </si>
+  <si>
+    <t>Butuh aturan due date yang eksak dari klien</t>
+  </si>
+  <si>
+    <t>12 payment term sudah tersedia</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Alamat AIM belum lengkap di Bill / Jurnal Voucher</t>
+  </si>
+  <si>
+    <t>Butuh alamat persis sesuai NPWP AIM</t>
+  </si>
+  <si>
+    <t>Company 1 street hanya 'Erajaya Plaza' (street2 &amp; zip kosong); company 2 lengkap</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Tambah nomor seri faktur pajak saat tarik GL</t>
+  </si>
+  <si>
+    <t>2 kolom opsional (No. FP Masukan / Keluaran), default OFF karena modul dipakai semua tenant</t>
+  </si>
+  <si>
+    <t>408 baris ber-NSFP di prd_levis_begbal; 17 di prd_arkaaim</t>
+  </si>
+  <si>
+    <t>849fadc</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Generate format impor PSIAP faktur keluaran</t>
+  </si>
+  <si>
+    <t>Butuh template impor PSIAP dari klien</t>
+  </si>
+  <si>
+    <t>0 hasil pencarian 'PSIAP' di seluruh source tree</t>
+  </si>
+  <si>
+    <t>FASHION (Levi's-EBR)</t>
+  </si>
+  <si>
+    <t>13 baris sheet dihitung 18 entri (item #1 berisi 6 sub-request) · database produksi: prd_levis_begbal</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Rekap PPh + Kode Objek, COA Expense, No/Tgl Invoice, No Dok Jurnal</t>
+  </si>
+  <si>
+    <t>SUDAH LIVE SEJAK AWAL — kelima kolom sudah ada. Nol development</t>
+  </si>
+  <si>
+    <t>Terverifikasi pada kode terpasang di /opt</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Report Import PPN Masukan (8 kolom)</t>
+  </si>
+  <si>
+    <t>Report sudah punya persis 8 kolom yang diminta; terblokir bug dispatcher</t>
+  </si>
+  <si>
+    <t>prd_levis_begbal 27 baris</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Report Ekualisasi Biaya vs Objek Pemotongan PPh</t>
+  </si>
+  <si>
+    <t>4 kolom ditambah + sumber data dilebarkan. Menambah kolom saja akan menyerahkan report yang tetap kosong: bill di-input tanpa produk</t>
+  </si>
+  <si>
+    <t>0 -&gt; 112 baris. PPN tepat 11% dari DPP per baris</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Report Upload Retur Pajak</t>
+  </si>
+  <si>
+    <t>Butuh template import Coretax dari klien</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Report Upload Faktur Pajak Keluaran</t>
+  </si>
+  <si>
+    <t>Butuh template XLS Mitra Pajakku. Modul yang ada adalah API adapter, bukan penulis template</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>Mapping COA jurnal PPh, tetap bisa diubah Accounting</t>
+  </si>
+  <si>
+    <t>SUDAH TERPENUHI — mapping configurable per rule</t>
+  </si>
+  <si>
+    <t>107 rule active, account_id NULL = 0</t>
+  </si>
+  <si>
+    <t>Jurnal PPh input manual tidak muncul di Rekap PPh</t>
+  </si>
+  <si>
+    <t>Kini menangkap PPh dari native tax &amp; jurnal manual, dengan kolom Sumber. 50 baris withholding tanpa jurnal GL sengaja dikecualikan + ditampilkan sbg note</t>
+  </si>
+  <si>
+    <t>50 -&gt; 105 baris; total 532.229.118,00 tie PERSIS ke GL credit</t>
+  </si>
+  <si>
+    <t>45b5f78</t>
+  </si>
+  <si>
+    <t>Report Import PPN Masukan keluar Trial Balance</t>
+  </si>
+  <si>
+    <t>Bug dispatcher yang sama dengan EO #5</t>
+  </si>
+  <si>
+    <t>Belum ada GL Open Items / Outstanding balance</t>
+  </si>
+  <si>
+    <t>Report baru, residual dihitung AS-OF per tanggal (bukan residual saat ini)</t>
+  </si>
+  <si>
+    <t>3.827 baris, 18.397.721.518,82 = saldo GL akun rekonsiliasi (selisih 0,00)</t>
+  </si>
+  <si>
+    <t>5465932</t>
+  </si>
+  <si>
+    <t>Report mapping vendor bill vs payment number</t>
+  </si>
+  <si>
+    <t>Satu report untuk item #5 dan #13. Bill tanpa alokasi tetap tampil 'Belum dibayar' sehingga sekaligus jadi daftar bill terhutang</t>
+  </si>
+  <si>
+    <t>151 baris (100 belum dibayar / 48 lunas / 3 batal); sisa -5.330.536.589,74 = jumlah residual bill (selisih 0,00)</t>
+  </si>
+  <si>
+    <t>On Hand Inventory report belum ada</t>
+  </si>
+  <si>
+    <t>Modul terinstall. CATATAN: akan tampil kosong sampai penerimaan barang dicatat di Odoo</t>
+  </si>
+  <si>
+    <t>prd_levis_begbal: 0 stock_quant, 0 purchase order</t>
+  </si>
+  <si>
+    <t>Purchase Return report belum ada</t>
+  </si>
+  <si>
+    <t>Modul terinstall. CATATAN: akan tampil kosong sampai retur dicatat di Odoo</t>
+  </si>
+  <si>
+    <t>0 pergerakan retur ke supplier</t>
+  </si>
+  <si>
+    <t>Bug dispatcher yang sama</t>
+  </si>
+  <si>
+    <t>prd_levis_begbal 69 baris</t>
+  </si>
+  <si>
+    <t>Sales report belum menampilkan data apapun</t>
+  </si>
+  <si>
+    <t>POS jadi sumber kedua. Revenue retail tidak lewat customer invoice: 16.064 order walk-in, revenue masuk GL lewat 860 jurnal penutup sesi</t>
+  </si>
+  <si>
+    <t>0 -&gt; 11.496 baris (Juni 2026); Sales Net 5.633.504.522,00 = revenue GL</t>
+  </si>
+  <si>
+    <t>ef10d55</t>
+  </si>
+  <si>
+    <t>Sales report detail layout X24DN (COGS &amp; margin)</t>
+  </si>
+  <si>
+    <t>17 kolom. Store/Register/Txn di-parse dari pos_reference. Diskon dari ri_src_discount (field discount bernilai 0 di semua baris). COGS sebasis levis.cogs.run agar konsisten dengan GL. CATATAN: MARGIN BELUM BERMAKNA sampai cost produk tersedia</t>
+  </si>
+  <si>
+    <t>Gross-Diskon-Total = 0,00; Net+Pajak-Total = 0,00; Net-COGS-Margin = 0,00. Diskon 1.234.678.813 = jumlah ri_src_discount</t>
+  </si>
+  <si>
+    <t>Keterangan jurnal PPh &amp; PPN hilang saat reset to draft</t>
+  </si>
+  <si>
+    <t>Label dipertahankan; jurnal PPh direverse di periodenya sendiri; withholding line dibersihkan agar re-post menghitung ulang</t>
+  </si>
+  <si>
+    <t>Uji: menggandakan nilai bill di draft memindahkan PPh 1.351.351,35 -&gt; 2.702.702,70 dengan jurnal baru (sebelumnya tetap basi)</t>
+  </si>
+  <si>
+    <t>Modul Petty Cash all store</t>
+  </si>
+  <si>
+    <t>SUDAH TER-DEPLOY sejak awal. Perlu config per-store + training</t>
+  </si>
+  <si>
+    <t>custom_petty_cash 19.0.0.4.0 terinstall; 0 record</t>
+  </si>
+  <si>
+    <t>Report payment bill</t>
+  </si>
+  <si>
+    <t>Dikerjakan bersama item #5 (permintaan identik)</t>
+  </si>
+  <si>
+    <t>Lihat item #5</t>
+  </si>
+  <si>
+    <t>Status Delivery — List Kendala System ODOO</t>
+  </si>
+  <si>
+    <t>Worksheet EO (ARKA-AIM) + FASHION (Levi's/EBR) · posisi 11 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Total permintaan</t>
+  </si>
+  <si>
+    <t>33 entri dari 28 baris sheet — item FASHION #1 dihitung 6 sub-request terpisah</t>
+  </si>
+  <si>
+    <t>Jumlah</t>
+  </si>
+  <si>
+    <t>Arti</t>
+  </si>
+  <si>
+    <t>Sudah selesai dan aktif di database produksi</t>
+  </si>
+  <si>
+    <t>Sebagian sudah aktif di produksi; sisanya menunggu keputusan klien</t>
+  </si>
+  <si>
+    <t>Ditahan menunggu keputusan / konfirmasi (EO #8 dan EO #9)</t>
+  </si>
+  <si>
+    <t>Menunggu nilai, dokumen, atau template dari klien</t>
+  </si>
+  <si>
     <t>Tidak Reproduce</t>
   </si>
   <si>
-    <t>TIDAK diubah. Perlu klien menunjukkan transaksi mana yang dimaksud</t>
-  </si>
-  <si>
-    <t>payment_account_id NULL di semua payment method line; payment posted langsung Dr BCA Main Bank / Cr Trade Receivables. Bank statement = 0</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Purchase report keluar Trial Balance</t>
-  </si>
-  <si>
-    <t>Report code tidak terdaftar di dispatcher sehingga jatuh ke fallback Trial Balance</t>
-  </si>
-  <si>
-    <t>prd_levis_begbal 69 baris; prd_arkaaim 9 baris</t>
-  </si>
-  <si>
-    <t>5a405ab</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Jurnal DP masuk ke COA penjualan</t>
-  </si>
-  <si>
-    <t>downpayment_account_id diarahkan ke 2108100001 Advances from customers</t>
-  </si>
-  <si>
-    <t>Diterapkan pada 2 company; re-run script melaporkan OK / 0 changes</t>
-  </si>
-  <si>
-    <t>8db557e</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Akses closing period belum tersedia</t>
-  </si>
-  <si>
-    <t>Butuh konfirmasi periode mana yang ditutup — lock date memblokir posting</t>
-  </si>
-  <si>
-    <t>fiscalyear_lock_date &amp; tax_lock_date NULL di kedua company</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Nilai perolehan asset selisih vs report accounting</t>
-  </si>
-  <si>
-    <t>Ditahan</t>
-  </si>
-  <si>
-    <t>DITAHAN menunggu konfirmasi. Ternyata DUA komponen, bukan satu</t>
-  </si>
-  <si>
-    <t>Perolehan: register 27.145.108.236 vs GL 27.110.131.391 = selisih 34.976.845. Accum-dep: 6.786.277.002,84 vs GL 7.341.288.299 = selisih +/- 555.011.296</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>No document depresiasi per bulan belum muncul</t>
-  </si>
-  <si>
-    <t>Kode SELESAI &amp; teruji. POSTING PRODUKSI DITAHAN menunggu keputusan klien. Akarnya bukan penomoran: jurnal belum pernah dibuat sama sekali</t>
-  </si>
-  <si>
-    <t>Uji di trn_arkaaim_begbal: 3.320 baris -&gt; 1 jurnal 565.523.083,57; GL accum-dep bergerak persis sebesar itu; reverse 1 baris tidak mengubah jurnal bulanan</t>
-  </si>
-  <si>
-    <t>d1c8952</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Sales report kosong padahal ada di detail beginning balance</t>
-  </si>
-  <si>
-    <t>Wizard dapat pilihan Sumber Data: Invoice+POS atau Akun Pendapatan (GL). Dibuat sebagai pilihan basis, bukan sumber ketiga, agar tidak double-count</t>
-  </si>
-  <si>
-    <t>Basis GL 735.585.585 = revenue GL independen (selisih 0,00); basis dokumen hanya 150.000.000</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PPh withholding belum otomatis per kode objek</t>
-  </si>
-  <si>
-    <t>Engine sudah ada tapi registry kosong; 107 kode objek dimuat + modul di-upgrade</t>
-  </si>
-  <si>
-    <t>107 kategori + 214 rule (107 x 2 company), 0 rule tanpa akun, 0 SKIP</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Setting due date belum sesuai ketentuan Erajaya</t>
-  </si>
-  <si>
-    <t>Butuh aturan due date yang eksak dari klien</t>
-  </si>
-  <si>
-    <t>12 payment term sudah tersedia</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Alamat AIM belum lengkap di Bill / Jurnal Voucher</t>
-  </si>
-  <si>
-    <t>Butuh alamat persis sesuai NPWP AIM</t>
-  </si>
-  <si>
-    <t>Company 1 street hanya 'Erajaya Plaza' (street2 &amp; zip kosong); company 2 lengkap</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Tambah nomor seri faktur pajak saat tarik GL</t>
-  </si>
-  <si>
-    <t>2 kolom opsional (No. FP Masukan / Keluaran), default OFF karena modul dipakai semua tenant</t>
-  </si>
-  <si>
-    <t>408 baris ber-NSFP di prd_levis_begbal; 17 di prd_arkaaim</t>
-  </si>
-  <si>
-    <t>849fadc</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Generate format impor PSIAP faktur keluaran</t>
-  </si>
-  <si>
-    <t>Butuh template impor PSIAP dari klien</t>
-  </si>
-  <si>
-    <t>0 hasil pencarian 'PSIAP' di seluruh source tree</t>
-  </si>
-  <si>
-    <t>FASHION (Levi's-EBR)</t>
-  </si>
-  <si>
-    <t>13 baris sheet dihitung 18 entri (item #1 berisi 6 sub-request) · database produksi: prd_levis_begbal</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>Rekap PPh + Kode Objek, COA Expense, No/Tgl Invoice, No Dok Jurnal</t>
-  </si>
-  <si>
-    <t>SUDAH LIVE SEJAK AWAL — kelima kolom sudah ada. Nol development</t>
-  </si>
-  <si>
-    <t>Terverifikasi pada kode terpasang di /opt</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>Report Import PPN Masukan (8 kolom)</t>
-  </si>
-  <si>
-    <t>Report sudah punya persis 8 kolom yang diminta; terblokir bug dispatcher</t>
-  </si>
-  <si>
-    <t>prd_levis_begbal 27 baris</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>Report Ekualisasi Biaya vs Objek Pemotongan PPh</t>
-  </si>
-  <si>
-    <t>4 kolom ditambah + sumber data dilebarkan. Menambah kolom saja akan menyerahkan report yang tetap kosong: bill di-input tanpa produk</t>
-  </si>
-  <si>
-    <t>0 -&gt; 112 baris. PPN tepat 11% dari DPP per baris</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>Report Upload Retur Pajak</t>
-  </si>
-  <si>
-    <t>Butuh template import Coretax dari klien</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>Report Upload Faktur Pajak Keluaran</t>
-  </si>
-  <si>
-    <t>Butuh template XLS Mitra Pajakku. Modul yang ada adalah API adapter, bukan penulis template</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>Mapping COA jurnal PPh, tetap bisa diubah Accounting</t>
-  </si>
-  <si>
-    <t>SUDAH TERPENUHI — mapping configurable per rule</t>
-  </si>
-  <si>
-    <t>107 rule active, account_id NULL = 0</t>
-  </si>
-  <si>
-    <t>Jurnal PPh input manual tidak muncul di Rekap PPh</t>
-  </si>
-  <si>
-    <t>Kini menangkap PPh dari native tax &amp; jurnal manual, dengan kolom Sumber. 50 baris withholding tanpa jurnal GL sengaja dikecualikan + ditampilkan sbg note</t>
-  </si>
-  <si>
-    <t>50 -&gt; 105 baris; total 532.229.118,00 tie PERSIS ke GL credit</t>
-  </si>
-  <si>
-    <t>45b5f78</t>
-  </si>
-  <si>
-    <t>Report Import PPN Masukan keluar Trial Balance</t>
-  </si>
-  <si>
-    <t>Bug dispatcher yang sama dengan EO #5</t>
-  </si>
-  <si>
-    <t>Belum ada GL Open Items / Outstanding balance</t>
-  </si>
-  <si>
-    <t>Report baru, residual dihitung AS-OF per tanggal (bukan residual saat ini)</t>
-  </si>
-  <si>
-    <t>3.827 baris, 18.397.721.518,82 = saldo GL akun rekonsiliasi (selisih 0,00)</t>
-  </si>
-  <si>
-    <t>5465932</t>
-  </si>
-  <si>
-    <t>Report mapping vendor bill vs payment number</t>
-  </si>
-  <si>
-    <t>Satu report untuk item #5 dan #13. Bill tanpa alokasi tetap tampil 'Belum dibayar' sehingga sekaligus jadi daftar bill terhutang</t>
-  </si>
-  <si>
-    <t>151 baris (100 belum dibayar / 48 lunas / 3 batal); sisa -5.330.536.589,74 = jumlah residual bill (selisih 0,00)</t>
-  </si>
-  <si>
-    <t>On Hand Inventory report belum ada</t>
-  </si>
-  <si>
-    <t>Modul terinstall. CATATAN: akan tampil kosong sampai penerimaan barang dicatat di Odoo</t>
-  </si>
-  <si>
-    <t>prd_levis_begbal: 0 stock_quant, 0 purchase order</t>
-  </si>
-  <si>
-    <t>Purchase Return report belum ada</t>
-  </si>
-  <si>
-    <t>Modul terinstall. CATATAN: akan tampil kosong sampai retur dicatat di Odoo</t>
-  </si>
-  <si>
-    <t>0 pergerakan retur ke supplier</t>
-  </si>
-  <si>
-    <t>Bug dispatcher yang sama</t>
-  </si>
-  <si>
-    <t>prd_levis_begbal 69 baris</t>
-  </si>
-  <si>
-    <t>Sales report belum menampilkan data apapun</t>
-  </si>
-  <si>
-    <t>POS jadi sumber kedua. Revenue retail tidak lewat customer invoice: 16.064 order walk-in, revenue masuk GL lewat 860 jurnal penutup sesi</t>
-  </si>
-  <si>
-    <t>0 -&gt; 11.496 baris (Juni 2026); Sales Net 5.633.504.522,00 = revenue GL</t>
-  </si>
-  <si>
-    <t>ef10d55</t>
-  </si>
-  <si>
-    <t>Sales report detail layout X24DN (COGS &amp; margin)</t>
-  </si>
-  <si>
-    <t>17 kolom. Store/Register/Txn di-parse dari pos_reference. Diskon dari ri_src_discount (field discount bernilai 0 di semua baris). COGS sebasis levis.cogs.run agar konsisten dengan GL. CATATAN: MARGIN BELUM BERMAKNA sampai cost produk tersedia</t>
-  </si>
-  <si>
-    <t>Gross-Diskon-Total = 0,00; Net+Pajak-Total = 0,00; Net-COGS-Margin = 0,00. Diskon 1.234.678.813 = jumlah ri_src_discount</t>
-  </si>
-  <si>
-    <t>Keterangan jurnal PPh &amp; PPN hilang saat reset to draft</t>
-  </si>
-  <si>
-    <t>Label dipertahankan; jurnal PPh direverse di periodenya sendiri; withholding line dibersihkan agar re-post menghitung ulang</t>
-  </si>
-  <si>
-    <t>Uji: menggandakan nilai bill di draft memindahkan PPh 1.351.351,35 -&gt; 2.702.702,70 dengan jurnal baru (sebelumnya tetap basi)</t>
-  </si>
-  <si>
-    <t>Modul Petty Cash all store</t>
-  </si>
-  <si>
-    <t>SUDAH TER-DEPLOY sejak awal. Perlu config per-store + training</t>
-  </si>
-  <si>
-    <t>custom_petty_cash 19.0.0.4.0 terinstall; 0 record</t>
-  </si>
-  <si>
-    <t>Report payment bill</t>
-  </si>
-  <si>
-    <t>Dikerjakan bersama item #5 (permintaan identik)</t>
-  </si>
-  <si>
-    <t>Lihat item #5</t>
-  </si>
-  <si>
-    <t>Status Delivery — List Kendala System ODOO</t>
-  </si>
-  <si>
-    <t>Worksheet EO (ARKA-AIM) + FASHION (Levi's/EBR) · posisi 30 Juli 2026</t>
-  </si>
-  <si>
-    <t>Total permintaan</t>
-  </si>
-  <si>
-    <t>33 entri dari 28 baris sheet — item FASHION #1 dihitung 6 sub-request terpisah</t>
-  </si>
-  <si>
-    <t>Jumlah</t>
-  </si>
-  <si>
-    <t>Arti</t>
-  </si>
-  <si>
-    <t>Sudah selesai dan aktif di database produksi</t>
-  </si>
-  <si>
-    <t>Ditahan menunggu keputusan / konfirmasi (EO #8 dan EO #9)</t>
-  </si>
-  <si>
-    <t>Menunggu nilai, dokumen, atau template dari klien</t>
-  </si>
-  <si>
     <t>Tidak dapat direproduksi di sistem — perlu klarifikasi klien</t>
   </si>
   <si>
@@ -475,10 +484,10 @@
     <t>Sisa development</t>
   </si>
   <si>
-    <t>NOL</t>
-  </si>
-  <si>
-    <t>Seluruh item yang belum tuntas kini menunggu keputusan atau data dari pihak lain, bukan menunggu pengerjaan.</t>
+    <t>1 item</t>
+  </si>
+  <si>
+    <t>Hampir semua yang belum tuntas menunggu keputusan atau data dari pihak lain. Satu pengecualian: akun 1106000001 (bernama Trade Receivables, bertipe liability_payable) perlu koreksi tipe — akun ini berisi data, jadi menunggu persetujuan Finance dulu karena saldo terposting akan berpindah antara AR dan AP.</t>
   </si>
   <si>
     <t>Perlu disampaikan</t>
@@ -523,7 +532,25 @@
     <t>EO #4</t>
   </si>
   <si>
-    <t>Transaksi mana yang menunjukkan COA perantara — tidak reproduce di sistem</t>
+    <t>Company 2 (ARKA) masih lewat COA perantara 1103000003/1103000004. Ikut dipindah ke langsung-ke-bank seperti company 1, atau tetap? Sudah ada 5 payment terposting lewat akun itu</t>
+  </si>
+  <si>
+    <t>EO #4 (b)</t>
+  </si>
+  <si>
+    <t>prd_arkaaim punya DUA journal bank aktif di satu rekening: BNK1 dan BCA2 sama-sama memakai 1103019280. Mana yang benar-benar dipakai?</t>
+  </si>
+  <si>
+    <t>EO #1 / #3</t>
+  </si>
+  <si>
+    <t>3 vendor company 1 diarahkan ke akun payable NON-TRADE (2103300001/2103400001). Kalau vendor dagang seharusnya ke 2103100001 Trade Payables, kirim daftar per-vendor</t>
+  </si>
+  <si>
+    <t>EO #3 (b)</t>
+  </si>
+  <si>
+    <t>Akun 1106000001 bernama Trade Receivables tetapi bertipe liability_payable — muncul di sisi AP, bukan AR. Akun ini BERISI DATA, jadi koreksi tipe memindahkan saldo terposting antar subledger AR/AP. Perlu persetujuan Finance</t>
   </si>
   <si>
     <t>EO #7</t>
@@ -662,6 +689,33 @@
   </si>
   <si>
     <t>trn_arkaaim_begbal saja — produksi sengaja belum (lihat EO #9)</t>
+  </si>
+  <si>
+    <t>custom_payment_methods_id</t>
+  </si>
+  <si>
+    <t>19.0.1.0.0</t>
+  </si>
+  <si>
+    <t>3 DB</t>
+  </si>
+  <si>
+    <t>Metode Giro + Bank Transfer — prd_arkaaim, trn_arkaaim, trn_arkaaim_begbal (11-Aug)</t>
+  </si>
+  <si>
+    <t>custom_payment_voucher</t>
+  </si>
+  <si>
+    <t>Printout Payment Voucher / Receipt — DB ARKA yang sama (11-Aug)</t>
+  </si>
+  <si>
+    <t>custom_levis_localization</t>
+  </si>
+  <si>
+    <t>19.0.1.25.1</t>
+  </si>
+  <si>
+    <t>Perbaikan voucher: kolom NOMOR DOC AP kini menyebut nomor bill — prd_levis_begbal, prd_levis, rnd_levis (11-Aug)</t>
   </si>
   <si>
     <t>Backup</t>
@@ -677,7 +731,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,6 +789,14 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FF5B3E9B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FFB4610C"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -763,7 +825,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -779,6 +841,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE8F7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -828,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -853,10 +921,13 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1153,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -1163,23 +1234,23 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="4">
         <v>33</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1187,10 +1258,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1">
@@ -1201,65 +1272,65 @@
         <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B9" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+    </row>
+    <row r="11" spans="1:3" ht="30" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>151</v>
       </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>153</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1270,11 +1341,22 @@
       <c r="A15" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>156</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1329,13 +1411,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1344,16 +1426,16 @@
       <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1362,10 +1444,10 @@
       <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1380,18 +1462,18 @@
       <c r="E7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1400,215 +1482,217 @@
       <c r="E8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="10" t="s">
-        <v>28</v>
+      <c r="A9" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="11" t="s">
         <v>32</v>
       </c>
+      <c r="F9" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10" t="s">
-        <v>33</v>
+      <c r="A10" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="11" t="s">
         <v>37</v>
       </c>
+      <c r="F10" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="10" t="s">
-        <v>38</v>
+      <c r="A11" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="11"/>
+        <v>42</v>
+      </c>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="10" t="s">
-        <v>42</v>
+      <c r="A12" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="C12" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="D12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="11" t="s">
         <v>51</v>
       </c>
+      <c r="F13" s="12" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10" t="s">
-        <v>52</v>
+      <c r="A14" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="10" t="s">
-        <v>56</v>
+      <c r="A15" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="11"/>
+        <v>60</v>
+      </c>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="10" t="s">
-        <v>60</v>
+      <c r="A16" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="11"/>
+        <v>64</v>
+      </c>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="10" t="s">
-        <v>64</v>
+      <c r="A17" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="11"/>
+        <v>68</v>
+      </c>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="10" t="s">
-        <v>68</v>
+      <c r="A18" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="11" t="s">
         <v>72</v>
       </c>
+      <c r="F18" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="10" t="s">
-        <v>73</v>
+      <c r="A19" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="F19" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F19"/>
@@ -1635,12 +1719,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28" customHeight="1">
@@ -1664,345 +1748,345 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="10" t="s">
-        <v>79</v>
+      <c r="A5" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="11"/>
+        <v>83</v>
+      </c>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="10" t="s">
-        <v>83</v>
+      <c r="A6" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>32</v>
+        <v>87</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="10" t="s">
-        <v>87</v>
+      <c r="A7" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>72</v>
+        <v>91</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10" t="s">
-        <v>91</v>
+      <c r="A8" s="11" t="s">
+        <v>92</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="11"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="10" t="s">
-        <v>94</v>
+      <c r="A9" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10" t="s">
-        <v>97</v>
+      <c r="A10" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="11"/>
+        <v>101</v>
+      </c>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="11" t="s">
         <v>104</v>
       </c>
+      <c r="F11" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>32</v>
+        <v>87</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="11" t="s">
         <v>110</v>
       </c>
+      <c r="F13" s="12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10" t="s">
-        <v>28</v>
+      <c r="A14" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="10" t="s">
-        <v>33</v>
+      <c r="A15" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="11"/>
+        <v>117</v>
+      </c>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="10" t="s">
-        <v>38</v>
+      <c r="A16" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="10" t="s">
-        <v>42</v>
+      <c r="A17" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>32</v>
+        <v>122</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="10" t="s">
-        <v>47</v>
+      <c r="A18" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="11" t="s">
         <v>125</v>
       </c>
+      <c r="F18" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="10" t="s">
-        <v>52</v>
+      <c r="A19" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="10" t="s">
-        <v>56</v>
+      <c r="A20" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>104</v>
+        <v>132</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="10" t="s">
-        <v>60</v>
+      <c r="A21" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="11"/>
+        <v>135</v>
+      </c>
+      <c r="F21" s="12"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="10" t="s">
-        <v>64</v>
+      <c r="A22" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>110</v>
+        <v>138</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2014,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -2028,154 +2112,178 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B20"/>
+  <autoFilter ref="A4:B23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.7109375" customWidth="1"/>
@@ -2186,96 +2294,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>200</v>
+      <c r="A5" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>209</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>204</v>
+      <c r="A6" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>208</v>
+      <c r="A7" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>211</v>
+      <c r="A8" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>212</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="3"/>
+      <c r="A10" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="5" t="s">
-        <v>214</v>
+      <c r="A11" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>215</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
